--- a/Dashboards/data/Data final/pobreza/pobreza_edad.xlsx
+++ b/Dashboards/data/Data final/pobreza/pobreza_edad.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="356" uniqueCount="10">
   <si>
     <t>anio</t>
   </si>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="1">
-        <v>6.760200023651123</v>
+        <v>6.7602000236511231</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
@@ -631,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="1">
-        <v>6.0232000350952148</v>
+        <v>6.0232000350952149</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -729,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="1">
-        <v>60.850601196289062</v>
+        <v>60.850601196289063</v>
       </c>
       <c r="D46" t="s">
         <v>8</v>
@@ -799,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="1">
-        <v>21.531499862670898</v>
+        <v>21.531499862670899</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
@@ -1051,7 +1051,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="1">
-        <v>5.7330999374389648</v>
+        <v>5.7330999374389649</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="C98" s="1">
-        <v>28.153600692749023</v>
+        <v>28.153600692749024</v>
       </c>
       <c r="D98" t="s">
         <v>8</v>
@@ -1821,7 +1821,7 @@
         <v>4</v>
       </c>
       <c r="C124" s="1">
-        <v>24.927099227905273</v>
+        <v>24.927099227905274</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -2437,7 +2437,7 @@
         <v>5</v>
       </c>
       <c r="C168" s="1">
-        <v>38.138198852539062</v>
+        <v>38.138198852539063</v>
       </c>
       <c r="D168" t="s">
         <v>8</v>
